--- a/lipid_pca_results.xlsx
+++ b/lipid_pca_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance Explained" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loadings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Variance Explained" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Loadings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scores" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/lipid_pca_results.xlsx
+++ b/lipid_pca_results.xlsx
@@ -447,13 +447,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5701668586570465</v>
+        <v>0.6571390239323702</v>
       </c>
       <c r="C2" t="n">
-        <v>57.01668586570465</v>
+        <v>65.71390239323702</v>
       </c>
       <c r="D2" t="n">
-        <v>57.01668586570465</v>
+        <v>65.71390239323702</v>
       </c>
     </row>
     <row r="3">
@@ -463,13 +463,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1828956985254745</v>
+        <v>0.1452968168468105</v>
       </c>
       <c r="C3" t="n">
-        <v>18.28956985254746</v>
+        <v>14.52968168468105</v>
       </c>
       <c r="D3" t="n">
-        <v>75.30625571825212</v>
+        <v>80.24358407791807</v>
       </c>
     </row>
     <row r="4">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1153219027774475</v>
+        <v>0.0875577346556243</v>
       </c>
       <c r="C4" t="n">
-        <v>11.53219027774475</v>
+        <v>8.755773465562431</v>
       </c>
       <c r="D4" t="n">
-        <v>86.83844599599686</v>
+        <v>88.9993575434805</v>
       </c>
     </row>
     <row r="5">
@@ -495,13 +495,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05000362306826363</v>
+        <v>0.05768552457920963</v>
       </c>
       <c r="C5" t="n">
-        <v>5.000362306826363</v>
+        <v>5.768552457920963</v>
       </c>
       <c r="D5" t="n">
-        <v>91.83880830282322</v>
+        <v>94.76791000140146</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0487627502735233</v>
+        <v>0.03084878757726652</v>
       </c>
       <c r="C6" t="n">
-        <v>4.87627502735233</v>
+        <v>3.084878757726652</v>
       </c>
       <c r="D6" t="n">
-        <v>96.71508333017556</v>
+        <v>97.85278875912812</v>
       </c>
     </row>
     <row r="7">
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02001452614189535</v>
+        <v>0.01136260882537952</v>
       </c>
       <c r="C7" t="n">
-        <v>2.001452614189535</v>
+        <v>1.136260882537952</v>
       </c>
       <c r="D7" t="n">
-        <v>98.71653594436509</v>
+        <v>98.98904964166607</v>
       </c>
     </row>
     <row r="8">
@@ -543,13 +543,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008043084797149748</v>
+        <v>0.007431360758141286</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8043084797149748</v>
+        <v>0.7431360758141285</v>
       </c>
       <c r="D8" t="n">
-        <v>99.52084442408007</v>
+        <v>99.73218571748021</v>
       </c>
     </row>
     <row r="9">
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003834312691902461</v>
+        <v>0.002417806995939088</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3834312691902461</v>
+        <v>0.2417806995939088</v>
       </c>
       <c r="D9" t="n">
-        <v>99.90427569327032</v>
+        <v>99.97396641707411</v>
       </c>
     </row>
     <row r="10">
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0009569007956143139</v>
+        <v>0.0002603081436993351</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09569007956143138</v>
+        <v>0.02603081436993351</v>
       </c>
       <c r="D10" t="n">
-        <v>99.99996577283174</v>
+        <v>99.99999723144406</v>
       </c>
     </row>
     <row r="11">
@@ -591,10 +591,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.422716826428123e-07</v>
+        <v>2.768555955510255e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>3.422716826428123e-05</v>
+        <v>2.768555955510255e-06</v>
       </c>
       <c r="D11" t="n">
         <v>100</v>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.576757485600053e-34</v>
+        <v>4.983258308185137e-33</v>
       </c>
       <c r="C12" t="n">
-        <v>8.576757485600053e-32</v>
+        <v>4.983258308185137e-31</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,717 +694,997 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.303468442050179</v>
+        <v>0.2556035005634808</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01278053871880766</v>
+        <v>0.01420902360254619</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01844063075853308</v>
+        <v>-0.03435646855223053</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1121627859016576</v>
+        <v>-0.00175341113820108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1216131983831112</v>
+        <v>-0.01859179457131108</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2393138884899523</v>
+        <v>0.165160164256385</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1486513294383822</v>
+        <v>-0.105838601258058</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2451322036642811</v>
+        <v>-0.0593265503964282</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2768025059835084</v>
+        <v>-0.0164975529423137</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4496911416078944</v>
+        <v>0.02547874846937695</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4435427517126427</v>
+        <v>0.5204505957363235</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rotatable_bond_count</t>
+          <t>logp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3080307718954967</v>
+        <v>0.2229860802438658</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02302903874334894</v>
+        <v>-0.06065552641786996</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09382431598830658</v>
+        <v>0.2555107717615562</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06086814722063921</v>
+        <v>-0.0004976053069374362</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02255014165491472</v>
+        <v>-2.551948247311733e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.02335940150047756</v>
+        <v>0.5497114768153328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04644571088170887</v>
+        <v>0.3879616784027287</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1585775722045198</v>
+        <v>-0.003633554101309865</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.09952217035686586</v>
+        <v>-0.04314817905445075</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.326187752992453</v>
+        <v>-0.05085971897151496</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.05226558062177622</v>
+        <v>-0.09421330218967072</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hbond_acceptor_count</t>
+          <t>rotatable_bond_count</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2618232809637886</v>
+        <v>0.2479171937391635</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2623451459866649</v>
+        <v>0.1301666984773731</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1661631908017519</v>
+        <v>0.08038316054507455</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.007448659794934854</v>
+        <v>-0.005483259082369147</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01150352338261122</v>
+        <v>0.009301278334105333</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1180742360493032</v>
+        <v>0.04666417526769501</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2012956062288753</v>
+        <v>0.05485274483592783</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1001823504386661</v>
+        <v>-0.06144740259377634</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2175349023667769</v>
+        <v>-0.03744870972161189</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2291289909410564</v>
+        <v>-0.1136297755050365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02324225861431264</v>
+        <v>-0.09657451556910547</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hbond_donor_count</t>
+          <t>hbond_acceptor_count</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07080925968710738</v>
+        <v>0.2295398603831304</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2952121992708019</v>
+        <v>0.1707103935246471</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4741136424457978</v>
+        <v>-0.2155444242595615</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05831444073936953</v>
+        <v>0.03915093685554458</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1920558134970803</v>
+        <v>-0.000294485345733373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6337833975181872</v>
+        <v>-0.1233634306057618</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2639569904564504</v>
+        <v>-0.1976757456686572</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2284301167986133</v>
+        <v>0.01391247437605983</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2631519096558815</v>
+        <v>0.03013283530546221</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1282632495625836</v>
+        <v>-0.01213580332166975</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.08804031724537539</v>
+        <v>-0.44239638602993</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>logp</t>
+          <t>hbond_donor_count</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.231472771585011</v>
+        <v>-0.05777122043855589</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2479178093837871</v>
+        <v>0.2114945889151186</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002651607514386152</v>
+        <v>-0.1890368275994598</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4335381821264307</v>
+        <v>0.6710650419832542</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01184467566592139</v>
+        <v>0.3727724804985232</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.23879916238826</v>
+        <v>0.0981490406337566</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6299176007483863</v>
+        <v>0.4130444354764531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07214308548894884</v>
+        <v>0.07946436324343123</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.07869004664216628</v>
+        <v>-0.0367419717701311</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4812862569876846</v>
+        <v>0.04930847215435251</v>
       </c>
       <c r="L6" t="n">
-        <v>3.20576898360514e-15</v>
+        <v>0.08530436075280208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tpsa</t>
+          <t>heavy_atom_count</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2400676364319075</v>
+        <v>0.25521640310978</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3058262024033774</v>
+        <v>-0.02404548851124937</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2081914061231658</v>
+        <v>-0.01272270837349486</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008683472285160894</v>
+        <v>0.006097172216896958</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.002893737572428168</v>
+        <v>-0.01692894855711394</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.06129715591910434</v>
+        <v>0.2010686144889861</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.179756285353938</v>
+        <v>-0.1185517555897592</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2117817478027947</v>
+        <v>-0.0303417872933264</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2882611938333794</v>
+        <v>-0.01044383394865982</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2713566192729275</v>
+        <v>0.07328027108634576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5024299767844864</v>
+        <v>-0.1651311270716397</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>formal_charge</t>
+          <t>tpsa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.006152524206115034</v>
+        <v>0.2011414525970814</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5020971279047972</v>
+        <v>0.2080144668334451</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2751087311641933</v>
+        <v>-0.2915701767298517</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02878503485462131</v>
+        <v>0.2061965763155478</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02338712291002581</v>
+        <v>0.07219343597327978</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04079393647246086</v>
+        <v>-0.004671466109622793</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2562763316045753</v>
+        <v>-0.1324318358804137</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1316664401146038</v>
+        <v>0.4105655847419118</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.03873390772441353</v>
+        <v>0.1931959374568553</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1007818814621808</v>
+        <v>0.1435566789196582</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.04507822672736329</v>
+        <v>0.01882651597820495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>number_of_tails</t>
+          <t>complexity</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.303444836339168</v>
+        <v>0.1852258841318675</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06264056031274619</v>
+        <v>-0.3280861905192343</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1102961262663953</v>
+        <v>-0.207066408134019</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.006422301902474666</v>
+        <v>0.06893439610867649</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.06937023192122301</v>
+        <v>-0.06497499688263536</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08536411232160614</v>
+        <v>0.1959763545015205</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1323009753494791</v>
+        <v>-0.3018028216226426</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.323463410171164</v>
+        <v>0.09318823771765319</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1032069948726517</v>
+        <v>0.01835246315443938</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06544705007788049</v>
+        <v>-0.002198725081470076</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.01414458247647737</v>
+        <v>0.3466237958544339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tail_length_mean</t>
+          <t>number_of_rings</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3020587691998277</v>
+        <v>-0.2425119384374842</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09384511117012853</v>
+        <v>-0.128876188721336</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09051104397755143</v>
+        <v>-0.1342605892408623</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1180438169995765</v>
+        <v>0.004136700069669427</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01773591303960829</v>
+        <v>-0.01348775985432</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05661224303016726</v>
+        <v>0.2655738623451345</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1448200499333507</v>
+        <v>-0.05429982698951469</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05788748516245175</v>
+        <v>0.0511740289991617</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1464082082414551</v>
+        <v>0.1033509965666298</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2812891915138387</v>
+        <v>0.03827697529801107</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2069480404652139</v>
+        <v>-0.4596893776800964</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tail_length_max</t>
+          <t>aromatic_ring_count</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3033495728062419</v>
+        <v>1.08368000043337e-17</v>
       </c>
       <c r="C11" t="n">
-        <v>0.09149368726137765</v>
+        <v>4.517393897661786e-18</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03456277215528532</v>
+        <v>9.520233609146836e-19</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001552783904586662</v>
+        <v>3.396434919235149e-18</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1042312978824955</v>
+        <v>-1.259590696623559e-19</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0964734545892303</v>
+        <v>2.08664950684643e-17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1021865321419647</v>
+        <v>-6.139290706861911e-17</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2030264220790649</v>
+        <v>1.218458487920778e-16</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6942717823796534</v>
+        <v>6.254061933004994e-17</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.196797261533233</v>
+        <v>4.636414598291513e-17</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4035296807078286</v>
+        <v>-0.05500174035691302</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>avg_double_bonds_per_tail</t>
+          <t>aliphatic_ring_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.127093948018257</v>
+        <v>-0.2425119384374842</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09778003629034011</v>
+        <v>-0.128876188721336</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2242439461819174</v>
+        <v>-0.1342605892408621</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6699796064486678</v>
+        <v>0.00413670006966945</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5743337257860317</v>
+        <v>-0.01348775985431996</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.07496446417903643</v>
+        <v>0.2655738623451344</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1194198486597974</v>
+        <v>-0.05429982698951477</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1030814696725546</v>
+        <v>0.05117402899916192</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.003706155946429979</v>
+        <v>0.1033509965666299</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2979993631913634</v>
+        <v>0.03827697529801116</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.009834116173798979</v>
+        <v>-0.2020082655271455</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>is_mixture</t>
+          <t>saturated_ring_count</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1015724726475993</v>
+        <v>-0.2425119384374842</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02473905745680843</v>
+        <v>-0.1288761887213359</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3447822408691942</v>
+        <v>-0.134260589240862</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5469208815295701</v>
+        <v>0.004136700069669477</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6173139205493033</v>
+        <v>-0.01348775985431994</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2886910777605589</v>
+        <v>0.2655738623451344</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2827094537546158</v>
+        <v>-0.05429982698951467</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009116590597495811</v>
+        <v>0.05117402899916161</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.04081213292171938</v>
+        <v>0.1033509965666298</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.06613126506341215</v>
+        <v>0.03827697529800671</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1032007862426148</v>
+        <v>0.1445608743106916</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Has tails</t>
+          <t>fraction_csp3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.303444836339168</v>
+        <v>-0.09321488012527882</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06264056031274619</v>
+        <v>0.4892033043554097</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1102961262663953</v>
+        <v>0.05238433664267547</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.006422301902474673</v>
+        <v>-0.1936571321977606</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.06937023192122301</v>
+        <v>-0.03776493382520019</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08536411232160614</v>
+        <v>0.1372505631562937</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1323009753494791</v>
+        <v>0.01652655129826559</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3234634101711641</v>
+        <v>-0.3505617641392257</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1032069948726514</v>
+        <v>0.3671346379888711</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06544705007787965</v>
+        <v>0.6088223798679272</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.09221655773508378</v>
+        <v>0.1063562598790001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>is_zwitterionic</t>
+          <t>heteroatom_count</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2336645575198925</v>
+        <v>0.2302026642304696</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.119467494760413</v>
+        <v>0.1645335919462708</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.383451029476239</v>
+        <v>-0.2168388900966099</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07090153351700754</v>
+        <v>0.02912944110079862</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2360664174559677</v>
+        <v>-0.01112460518559705</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02070484166640124</v>
+        <v>-0.09638964728492459</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3041296854401518</v>
+        <v>-0.2307130135771585</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5130828753647771</v>
+        <v>0.1409199267774043</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3650414850922874</v>
+        <v>0.09084013557962438</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2679088694810423</v>
+        <v>0.03590719627135964</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3422959090123768</v>
+        <v>-0.0430055456107649</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>is_cationic</t>
+          <t>formal_charge</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.006152524206115034</v>
+        <v>-0.00288434694903446</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5020971279047972</v>
+        <v>-0.05793965131579363</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2751087311641933</v>
+        <v>0.6847460913297543</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02878503485462099</v>
+        <v>0.07632558918688351</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02338712291002593</v>
+        <v>0.1358342235600414</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04079393647246082</v>
+        <v>-0.02749545848096498</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2562763316045752</v>
+        <v>-0.1711603807898474</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1316664401146041</v>
+        <v>0.5717527175318495</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.038733907724413</v>
+        <v>0.1888151760537678</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1007818814621889</v>
+        <v>0.2338167734379544</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2147379636210626</v>
+        <v>-0.02238983389044783</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>is_anionic</t>
+          <t>atom_count</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.1282296663891995</v>
+        <v>0.25521640310978</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.2406636936563694</v>
+        <v>-0.02404548851124938</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4182475487431037</v>
+        <v>-0.01272270837349489</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1513443162698582</v>
+        <v>0.006097172216896944</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3853724975722133</v>
+        <v>-0.01692894855711395</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5800174529590765</v>
+        <v>0.2010686144889861</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.178596963085324</v>
+        <v>-0.1185517555897592</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04569345342018329</v>
+        <v>-0.03034178729332649</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1735951438362694</v>
+        <v>-0.01044383394865984</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.03343682914026409</v>
+        <v>0.07328027108634573</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3690846938449649</v>
+        <v>-0.2094449971177721</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>is_phospholipid</t>
+          <t>amide_bond_count</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2667623742148344</v>
+        <v>-0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.269853985887513</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08206267508014795</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02414253670030746</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.07517270603457016</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.04759511707800497</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05084965512383406</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3651178520393533</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.06437724948293583</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.008375616780276943</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06824845583866668</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>is_sterol</t>
+          <t>defined_atom_stereocenter_count</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.303444836339168</v>
+        <v>-0.2342381539305562</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.06264056031274619</v>
+        <v>-0.1438484311900963</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1102961262663953</v>
+        <v>-0.189506484008839</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006422301902474673</v>
+        <v>-0.06137051178396026</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06937023192122301</v>
+        <v>-0.07333620963124866</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.08536411232160614</v>
+        <v>0.2705734266725613</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1323009753494791</v>
+        <v>0.03745594047590965</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3234634101711641</v>
+        <v>0.1323956139525493</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1032069948726514</v>
+        <v>0.1219122219334768</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06544705007787965</v>
+        <v>0.06292925754404406</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09221655773508378</v>
+        <v>0.0574495047789435</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>defined_bond_stereocenter_count</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1328938145398982</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.4482807927697013</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.0230958790291815</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1764441208134749</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.002915923405020477</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.2379628636093783</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1113247006623736</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.1625387253155048</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.3516625142955312</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.6508674939786279</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.1150612025004549</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>molar_refractivity</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.2538649457059964</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.05017746462352481</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.05016310480453674</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8.340169255490982e-05</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.01705340918162722</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2117875453439621</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.003918962292184348</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.09386785537848123</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.06660079293279342</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.05606309209641898</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.001118010561163041</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>labute_surface_area</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2552914894215189</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.01961961462652067</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.008316521875730076</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.008625014036202047</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.02067887136885072</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2084924434821336</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.09520237627892268</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.06158950269888222</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.02273072658011515</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.04244466869701443</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.06327749666688365</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tail_length_mean</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.248661234771073</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.04373370640262505</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1539501920632039</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.04650012091292342</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.0004251046538856739</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.0463231367338595</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1858830600497695</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.174736724703745</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.2232971885998896</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.2625753751257622</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.07359917645047243</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>avg_double_bonds_per_tail</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.138396457604981</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.445327757031058</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.03160313551427945</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1263662112112732</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.06973732736138614</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.2199852977005752</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1283577544017705</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.2066248817852106</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7404892746851701</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.04523648861629641</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.009855660250200036</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>is_mixture</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.07903600837242238</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.09321087106820033</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.1401118146960646</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.505076198926942</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8379261052677158</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.007638047669504192</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.04061540715003487</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.03811235452871003</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.03846502049439255</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.02110237816081068</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.005547928459864851</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>is_zwitterionic</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1868392108232323</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.01388691805134101</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.2461385502314107</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.3851334068615128</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.3420031992044694</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.1224507487122199</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5671558783450799</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4453685598448495</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.04943497177555089</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1221886955997025</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.02241208758862623</v>
       </c>
     </row>
   </sheetData>
@@ -1490,37 +1770,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.449115777406512</v>
+        <v>1.174123364416258</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3239869475039123</v>
+        <v>1.516592141270074</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3083631114716324</v>
+        <v>-0.05649049319926389</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3130940559065649</v>
+        <v>-0.7494066754114596</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.276390659464006</v>
+        <v>-0.9594813565126658</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3501475948134686</v>
+        <v>-0.04323752433797694</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.004356790578347982</v>
+        <v>-0.1143942836291972</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06944121384193826</v>
+        <v>-0.02870859419672603</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.01784584176014727</v>
+        <v>-0.01916811525987744</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006717251555692307</v>
+        <v>0.002161656825208728</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.242504063336577e-16</v>
+        <v>3.38548284722045e-16</v>
       </c>
     </row>
     <row r="3">
@@ -1530,397 +1810,397 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.053822010604669</v>
+        <v>2.220105388749555</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03976649489815079</v>
+        <v>1.369752675615351</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2369833058128962</v>
+        <v>0.1927728059333944</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6299494209578145</v>
+        <v>-0.7222240004474374</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.186296261777424</v>
+        <v>-1.024814984728537</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6266139361120229</v>
+        <v>1.038061811422432</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6997494557122411</v>
+        <v>0.01453832253753152</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2229349590639888</v>
+        <v>-0.2239576843758192</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.08599849364625681</v>
+        <v>-0.04661304037542935</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.003417498372591894</v>
+        <v>-0.001079864085946442</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.242504063336641e-16</v>
+        <v>3.385482847220877e-16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHEMS</t>
+          <t>DMPC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.306196686807309</v>
+        <v>0.1297372700319535</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.090360870858915</v>
+        <v>1.657157683044026</v>
       </c>
       <c r="D4" t="n">
-        <v>0.306107624724094</v>
+        <v>-0.3069867221928673</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1337947945363867</v>
+        <v>-0.7743046279138273</v>
       </c>
       <c r="F4" t="n">
-        <v>0.661913826871294</v>
+        <v>-0.893958104563682</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.010004874965046</v>
+        <v>-1.125357095650893</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3787526383142526</v>
+        <v>-0.2444876075335904</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2974537861700138</v>
+        <v>0.1705732222710441</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.04052404583515625</v>
+        <v>0.004431828538975471</v>
       </c>
       <c r="K4" t="n">
-        <v>8.112734313000967e-06</v>
+        <v>-0.001079484026508382</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.242504063336618e-16</v>
+        <v>3.385482847220883e-16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DOPE</t>
+          <t>DAPC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.608664226116004</v>
+        <v>4.396307985870004</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.389656896051433</v>
+        <v>-4.159608116046099</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7195540849338633</v>
+        <v>-0.6645438282547311</v>
       </c>
       <c r="E5" t="n">
-        <v>0.936592812214241</v>
+        <v>1.142640404907897</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3811268803009142</v>
+        <v>-0.8429760412176971</v>
       </c>
       <c r="G5" t="n">
-        <v>1.109613196162981</v>
+        <v>-0.1917757486064187</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2384195975396531</v>
+        <v>-0.1436235263009507</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5037935359649987</v>
+        <v>-0.1791125283006072</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.06993727263815691</v>
+        <v>0.05474049292913567</v>
       </c>
       <c r="K5" t="n">
-        <v>1.859086587077297e-05</v>
+        <v>-3.550302327078411e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.242504063336619e-16</v>
+        <v>3.385482847220737e-16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chol</t>
+          <t>Egg PC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6.906470000291371</v>
+        <v>2.10495613722789</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2154418001905301</v>
+        <v>0.3159214127469593</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.277468969821985</v>
+        <v>-0.4476001598987063</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1583193389103567</v>
+        <v>-1.751668519356314</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4035866508040568</v>
+        <v>1.243506971985401</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8795292461529873</v>
+        <v>0.1256033502041734</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4600159376586274</v>
+        <v>0.07563808833326686</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.202738201244037</v>
+        <v>-0.06396082733497072</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04806601592969786</v>
+        <v>0.1715915395162613</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.823418353464237e-06</v>
+        <v>-1.16423022840359e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.242504063336619e-16</v>
+        <v>3.385482847220734e-16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DMPC</t>
+          <t>Soy PC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8347118260773991</v>
+        <v>2.963157516560816</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6185940949186811</v>
+        <v>-1.637481016363172</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3796318261277739</v>
+        <v>-0.7495079232901176</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02192470287985746</v>
+        <v>-1.091403350594017</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.366981298350683</v>
+        <v>1.278857899780853</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.06367659097558902</v>
+        <v>-0.1171344988771279</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7348538874901919</v>
+        <v>-0.04618551509796041</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3648398731655064</v>
+        <v>0.072952727951035</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0536035861865859</v>
+        <v>-0.1725685918173522</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.003311832165273218</v>
+        <v>1.169931198932093e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.242504063336639e-16</v>
+        <v>3.385482847220737e-16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DAPC</t>
+          <t>DOPE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.320546873054276</v>
+        <v>1.954417517050185</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.05468987479740232</v>
+        <v>0.6920988871620657</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9699838831758314</v>
+        <v>-0.5905392917791863</v>
       </c>
       <c r="E8" t="n">
-        <v>2.410709745239174</v>
+        <v>1.242502482784385</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8155730436871779</v>
+        <v>-0.08516423578829284</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5498979784441366</v>
+        <v>0.1445048539269117</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2185419070095594</v>
+        <v>0.9714675926719263</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1077354625830646</v>
+        <v>0.3832670068414538</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08988981350917481</v>
+        <v>0.009152020393987206</v>
       </c>
       <c r="K8" t="n">
-        <v>3.950612155129758e-06</v>
+        <v>1.59628965013648e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.242504063336619e-16</v>
+        <v>3.385482847220732e-16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DOTAP</t>
+          <t>DPPG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1996768910736793</v>
+        <v>0.7459151075993213</v>
       </c>
       <c r="C9" t="n">
-        <v>5.22713520594541</v>
+        <v>2.685088614992107</v>
       </c>
       <c r="D9" t="n">
-        <v>1.80587912777838</v>
+        <v>-0.5906457436019437</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08192958170033669</v>
+        <v>2.36034672959284</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06491386911390749</v>
+        <v>1.019859291863761</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04647436159188304</v>
+        <v>-0.1024028766158656</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1173285359034211</v>
+        <v>-0.3810648473979902</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02873658299581087</v>
+        <v>-0.2436712399644497</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0021097487312415</v>
+        <v>-0.007766164900288791</v>
       </c>
       <c r="K9" t="n">
-        <v>1.963477535493909e-06</v>
+        <v>-9.859400501934545e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.242504063336619e-16</v>
+        <v>3.385482847220737e-16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Soy PC</t>
+          <t>CHEMS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.992727428240827</v>
+        <v>-6.754783450517986</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2574731279471472</v>
+        <v>-1.016501157753769</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.713821782370151</v>
+        <v>-1.04415447899295</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6642569700918169</v>
+        <v>0.2652885684744292</v>
       </c>
       <c r="F10" t="n">
-        <v>1.366447307046913</v>
+        <v>-0.04540101970839081</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2480606313448637</v>
+        <v>0.5873196385592272</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1180266682505959</v>
+        <v>-0.6029063099218945</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1975627484976627</v>
+        <v>0.3759577222393693</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.28536703538318</v>
+        <v>0.02273377322574712</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.055007817263395e-05</v>
+        <v>1.688908609579153e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.242504063336618e-16</v>
+        <v>3.385482847220736e-16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egg PC</t>
+          <t>DOTAP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.429965150311214</v>
+        <v>-0.1378581967701359</v>
       </c>
       <c r="C11" t="n">
-        <v>0.08806454047818534</v>
+        <v>-0.6122937313919028</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.322623400189309</v>
+        <v>4.360656872434427</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.424244260744804</v>
+        <v>0.3202320885669762</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9323623902248037</v>
+        <v>0.3047720530852476</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1931921255669665</v>
+        <v>-0.02272306221545298</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.05562211179248002</v>
+        <v>-0.09251228860433641</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2002322411939637</v>
+        <v>0.1005443575356628</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2823846417346693</v>
+        <v>0.003574806089287779</v>
       </c>
       <c r="K11" t="n">
-        <v>8.821509817218685e-06</v>
+        <v>4.708220616461222e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.24250406333662e-16</v>
+        <v>3.385482847220734e-16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DPPG</t>
+          <t>Chol</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7227902863614556</v>
+        <v>-8.796078640217853</v>
       </c>
       <c r="C12" t="n">
-        <v>-2.271059495532775</v>
+        <v>-0.8107273932756384</v>
       </c>
       <c r="D12" t="n">
-        <v>3.37733544153324</v>
+        <v>-0.1029610371580561</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4441366787065787</v>
+        <v>-0.2420031006034718</v>
       </c>
       <c r="F12" t="n">
-        <v>0.77317131375299</v>
+        <v>0.004799525804001449</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1234714144905817</v>
+        <v>-0.2928588478090066</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2690529294885146</v>
+        <v>0.5635303749431967</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3108336060565672</v>
+        <v>-0.3638841626659921</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02783838063401076</v>
+        <v>-0.02010854834044644</v>
       </c>
       <c r="K12" t="n">
-        <v>-8.986720992367856e-06</v>
+        <v>-1.585500403003088e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.242504063336619e-16</v>
+        <v>3.385482847220736e-16</v>
       </c>
     </row>
   </sheetData>
